--- a/output/pdf_financials_xlsx/MANU.xlsx
+++ b/output/pdf_financials_xlsx/MANU.xlsx
@@ -5458,10 +5458,10 @@
         <v>2.536451</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.644902</v>
+        <v>2.533069</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.603698</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -5476,25 +5476,25 @@
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.216299</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.409146</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.394772</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.394772</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.359216</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.686721</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.22392</v>
       </c>
     </row>
     <row r="93">
@@ -9255,7 +9255,11 @@
           <t>Reserve (Note 12) 1,271,936</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10757,7 +10761,11 @@
           <t>Reserve (Note 9) 1,223,920</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12168,7 +12176,11 @@
           <t>Reserve (Note 9) 1,686,721</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -13651,7 +13663,11 @@
           <t>Share-based payment reserve (note 9)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -14561,7 +14577,11 @@
           <t>Share-based payment reserve (note 9)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -15461,7 +15481,11 @@
           <t>Share-based payment reserve (note 10)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -18446,7 +18470,11 @@
           <t>Reserves (note 10) 2,603,816</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MANU.xlsx
+++ b/output/pdf_financials_xlsx/MANU.xlsx
@@ -1017,40 +1017,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.021253</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-8.3e-05</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001982</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.074755</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.04357</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.011701</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000292</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000253</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000261</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000261</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1937,40 +1937,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-9.406898</v>
+        <v>-9.385645</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.822716</v>
+        <v>-1.822633</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.258895</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.367387</v>
+        <v>4.365405</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.283169</v>
+        <v>-0.357924</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.26561</v>
+        <v>-1.30918</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.832377</v>
+        <v>-0.844078</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.6424029999999999</v>
+        <v>-0.643003</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.672274</v>
+        <v>-0.672566</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.351874</v>
+        <v>-1.352127</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-10.435322</v>
+        <v>-10.435583</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.203177</v>
+        <v>-0.203438</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2053,40 +2053,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-9.155524</v>
+        <v>-9.134271</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.753735</v>
+        <v>-1.753652</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0.594955</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.367387</v>
+        <v>4.365405</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.283169</v>
+        <v>-0.357924</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.26561</v>
+        <v>-1.30918</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.832377</v>
+        <v>-0.844078</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.6424029999999999</v>
+        <v>-0.643003</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.672274</v>
+        <v>-0.672566</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.351874</v>
+        <v>-1.352127</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-10.435322</v>
+        <v>-10.435583</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.203177</v>
+        <v>-0.203438</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-214.3290491825998</v>
+        <v>-213.8315205559174</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-40.24837966612665</v>
+        <v>-40.24647480848722</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>12.72237778911117</v>
@@ -2355,22 +2355,22 @@
         <v>0.00746</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.128911</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.024667</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000581</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.086975</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.713638</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.125176</v>
       </c>
     </row>
     <row r="35">
@@ -2459,22 +2459,22 @@
         <v>0.00746</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.128911</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.024667</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000581</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.086975</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.713638</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.125176</v>
       </c>
     </row>
     <row r="37">
@@ -3083,22 +3083,22 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.138287</v>
+        <v>0.009376000000000001</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.030454</v>
+        <v>0.005787</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000581</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.619074</v>
+        <v>0.532099</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.868038</v>
+        <v>0.1544</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.359944</v>
+        <v>0.234768</v>
       </c>
     </row>
     <row r="49">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -36280,7 +36280,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -43788,7 +43788,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -47756,7 +47756,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E441" s="5" t="n">
@@ -47849,7 +47849,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E442" s="5" t="n">
